--- a/testProject/src/test/resources/data/register/register.xlsx
+++ b/testProject/src/test/resources/data/register/register.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\Desktop\Automation\TestProject\Workspace\testProject\src\test\resources\data\register\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\Desktop\Automation\TestProject\testProject\src\test\resources\data\register\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10535A4-D878-40EF-987D-714912105786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A2C858-436B-45AB-B0A4-AC909DA5C89C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="3930" windowWidth="21495" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -33,23 +33,15 @@
     <t>password</t>
   </si>
   <si>
-    <t>pese120799939989898</t>
+    <t>ricardito1990123453522</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -77,9 +69,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -360,13 +351,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -374,16 +365,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2">
-        <v>12345</v>
+        <v>123</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E7" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
